--- a/Plan de test PCB Velux V3.xlsx
+++ b/Plan de test PCB Velux V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Louison-M\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64F19805-FE90-4704-A6CA-F91A24D400B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF7CBE5-F85A-4F75-85A3-D9C1138C5383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="15" xr2:uid="{019B3536-79B6-4D88-9C35-6E4C40FF7309}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{019B3536-79B6-4D88-9C35-6E4C40FF7309}"/>
   </bookViews>
   <sheets>
     <sheet name="ID Point de test" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="FT Ethernet" sheetId="25" r:id="rId14"/>
     <sheet name="PT Ethernet" sheetId="27" r:id="rId15"/>
     <sheet name="PV Ethernet" sheetId="26" r:id="rId16"/>
+    <sheet name="FA Ethernet " sheetId="29" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="246">
   <si>
     <t>Nom Point de test</t>
   </si>
@@ -724,9 +725,6 @@
     <t>Communication Ethernet</t>
   </si>
   <si>
-    <t xml:space="preserve">Le but du test est de tester la communication Ethernet entre les appareils de mesure et le module ethernet pour vérifier ainsi que les bonne valeur sont envoyé et que le test est fiable </t>
-  </si>
-  <si>
     <t>Wireshark</t>
   </si>
   <si>
@@ -736,58 +734,139 @@
     <t xml:space="preserve">Arduino programmé pour communication avec la charger et le multimètre </t>
   </si>
   <si>
-    <t>➢Brancher la charge, le multiètre, le module ethernet et le pc au HUB Ethernet
- ➢Ouvrer l'application Wireshark et suivre la procédure d'utilisation à wireshark</t>
+    <t>Le but du test est de tester la communication Ethernet entre les appareils de mesure et le module ethernet</t>
+  </si>
+  <si>
+    <t>Intégration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB alimenté/ Arduino programmé pour communication avec la charger et le multimètre </t>
+  </si>
+  <si>
+    <t>HUB Ethernet</t>
+  </si>
+  <si>
+    <t>opérateur</t>
+  </si>
+  <si>
+    <t>La charge, le multiètre et le module ethernet sont connecté au HUB avec des cable RJ45</t>
+  </si>
+  <si>
+    <t>Obtention de la communication entre les appareils de mesure et le module ethernet</t>
+  </si>
+  <si>
+    <t>Tester communication ethernet</t>
+  </si>
+  <si>
+    <t>Ethernet OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+➢Observer la communication entre les appareils de mesure et le module Ethernet
+</t>
   </si>
   <si>
     <t xml:space="preserve">
 ➢ Obtenir la communication entre la charge et le module Ethernet
-➢ Obtenir la communication entre le multiètre et le module Ethernet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-➢Voir la communication entre les appareils de mesure et le module Ethernet
-</t>
-  </si>
-  <si>
-    <t>➢J'ai obtenue la communication entre le module ethernet et les appareils de mesure</t>
-  </si>
-  <si>
-    <t>Le test de la communication ethernet est réussi</t>
-  </si>
-  <si>
-    <t>Le but du test est de tester la communication Ethernet entre les appareils de mesure et le module ethernet</t>
-  </si>
-  <si>
-    <t>Intégration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCB alimenté/ Arduino programmé pour communication avec la charger et le multimètre </t>
-  </si>
-  <si>
-    <t>HUB Ethernet</t>
-  </si>
-  <si>
-    <t>opérateur</t>
-  </si>
-  <si>
-    <t>La charge, le multiètre et le module ethernet sont connecté au HUB avec des cable RJ45</t>
-  </si>
-  <si>
-    <t>Obtention de la communication entre les appareils de mesure et le module ethernet</t>
-  </si>
-  <si>
-    <t>Tester communication ethernet</t>
-  </si>
-  <si>
-    <t>Ethernet OK</t>
+➢ Obtenir la communication entre le multimètre et le module Ethernet</t>
+  </si>
+  <si>
+    <t>Le test de la communication Ethernet est réussi</t>
+  </si>
+  <si>
+    <t>➢Brancher la charge, le multimètre, le module Ethernet et le pc au HUB Ethernet
+ ➢Ouvrer l'application Wireshark et suivre la procédure d'utilisation à Wireshark</t>
+  </si>
+  <si>
+    <t>➢J'ai obtenu la communication entre le module Ethernet et les appareils de mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le but du test est de tester la communication Ethernet entre les appareils de mesure et le module Ethernet pour vérifier ainsi que les bonnes valeurs sont envoyé et que le test est fiable </t>
+  </si>
+  <si>
+    <t>Référence anomalie</t>
+  </si>
+  <si>
+    <t>Mesure intensité de court-circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditions d'apparition de l'anomalie  (environnement, paramètres...) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numéro de version du logiciel </t>
+  </si>
+  <si>
+    <t>Programme_Projet_Velux_V5</t>
+  </si>
+  <si>
+    <t>Version du système d’exploitation</t>
+  </si>
+  <si>
+    <t>Test intégration</t>
+  </si>
+  <si>
+    <t>Reproductibilité</t>
+  </si>
+  <si>
+    <t>Systématique    [X]
+Aléatoire	           []</t>
+  </si>
+  <si>
+    <t>Description du contexte dans lequel se produit l'anomalie</t>
+  </si>
+  <si>
+    <t>Au démarrage du système, si un panneau solaire est testé positivement avec un FF de 0,80, ce même panneau peut avoir un FF égal à «inf» ou supérieur à 1 lorsqu’il est testé après un panneau solaire testé négativement.</t>
+  </si>
+  <si>
+    <t>Description de l'anomalie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etat attendu </t>
+  </si>
+  <si>
+    <t>Lorsque les panneaux solaires sont testés successivement, les résultats doivent rester fiables et corrects, avec un Fill Factor compris entre 0 et 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etat constaté </t>
+  </si>
+  <si>
+    <t>Lorsqu’un panneau fonctionnel est testé après un panneau H.S., il peut présenter un Fill Factor supérieur à 1 ou égal à « inf », en raison d’une mesure faussée du courant de court-circuit. En revanche, lorsque ce même panneau solaire est testé en premier au démarrage du système, la mesure est correcte.</t>
+  </si>
+  <si>
+    <t>Classement proposé</t>
+  </si>
+  <si>
+    <t>[ ] mineure   [ ] majeure   [X] bloquante</t>
+  </si>
+  <si>
+    <t>Pièces jointes</t>
+  </si>
+  <si>
+    <t>Fichier de traces      [ ]
+Copie(s) d’écrans    [X]
+Autres                      [ ]</t>
+  </si>
+  <si>
+    <t>Clôture de la fiche d’anomalie</t>
+  </si>
+  <si>
+    <t>Date de la correction :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date de validation de la correction </t>
+  </si>
+  <si>
+    <t>Version corrigeant l’anomalie :</t>
+  </si>
+  <si>
+    <t>Voir modification dans rapport d'anomalie</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -853,6 +932,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -879,7 +965,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1490,11 +1576,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1664,17 +1765,80 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1691,72 +1855,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1883,32 +1984,125 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1935,6 +2129,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>696446</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>574303</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>132620</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>83751</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{447115F4-9D1C-4DC3-8E92-1581A05AEA68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12250271" y="2479303"/>
+          <a:ext cx="2788974" cy="1900223"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2474,60 +2717,60 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="3:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="138"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="131"/>
+      <c r="E4" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
       <c r="H4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="67"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="77" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="3:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="58"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="59" t="s">
         <v>37</v>
       </c>
       <c r="F6" s="60"/>
-      <c r="G6" s="130"/>
+      <c r="G6" s="132"/>
       <c r="H6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="137">
+      <c r="I6" s="130">
         <v>46087</v>
       </c>
-      <c r="J6" s="70"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="134" t="s">
+      <c r="C7" s="133" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="135"/>
+      <c r="D7" s="134"/>
       <c r="E7" s="14" t="s">
         <v>34</v>
       </c>
@@ -2548,28 +2791,28 @@
       </c>
     </row>
     <row r="8" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="85" t="s">
+      <c r="D8" s="78"/>
+      <c r="E8" s="79" t="s">
         <v>192</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="87"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="131"/>
-      <c r="F9" s="76" t="s">
+      <c r="E9" s="135"/>
+      <c r="F9" s="68" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="136"/>
@@ -2587,14 +2830,14 @@
       <c r="C10" s="49">
         <v>1</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="57" t="s">
         <v>193</v>
       </c>
-      <c r="E10" s="67"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="130"/>
+      <c r="G10" s="132"/>
       <c r="H10" s="8" t="s">
         <v>176</v>
       </c>
@@ -2609,14 +2852,14 @@
       <c r="C11" s="49">
         <v>2</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="57" t="s">
         <v>194</v>
       </c>
-      <c r="E11" s="67"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="G11" s="130"/>
+      <c r="G11" s="132"/>
       <c r="H11" s="8" t="s">
         <v>179</v>
       </c>
@@ -2631,14 +2874,14 @@
       <c r="C12" s="49">
         <v>3</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="E12" s="67"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="G12" s="130"/>
+      <c r="G12" s="132"/>
       <c r="H12" s="8" t="s">
         <v>182</v>
       </c>
@@ -2653,47 +2896,34 @@
       <c r="C13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
-      <c r="G13" s="64"/>
-      <c r="H13" s="65"/>
+      <c r="E13" s="85"/>
+      <c r="F13" s="85"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="86"/>
       <c r="I13" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="131"/>
-      <c r="E14" s="132" t="s">
+      <c r="D14" s="135"/>
+      <c r="E14" s="137" t="s">
         <v>145</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="61"/>
-      <c r="J14" s="133"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:J8"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="C14:D14"/>
@@ -2703,6 +2933,19 @@
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:J8"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:J5"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3090,42 +3333,42 @@
   <sheetData>
     <row r="2" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71" t="s">
+      <c r="B3" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="73" t="s">
+      <c r="C3" s="64"/>
+      <c r="D3" s="65" t="s">
         <v>201</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="67"/>
       <c r="G3" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="66" t="s">
+      <c r="H3" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="I3" s="67"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" spans="2:9" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="77" t="s">
-        <v>203</v>
-      </c>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="79"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="58"/>
+      <c r="C5" s="69"/>
       <c r="D5" s="59" t="s">
         <v>37</v>
       </c>
@@ -3134,27 +3377,27 @@
       <c r="G5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="69">
-        <v>46160</v>
-      </c>
-      <c r="I5" s="70"/>
+      <c r="H5" s="61">
+        <v>46132</v>
+      </c>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="2:9" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="81"/>
+      <c r="C6" s="74"/>
       <c r="D6" s="52" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="54" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F6" s="52" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H6" s="51" t="s">
         <v>31</v>
@@ -3162,31 +3405,31 @@
       <c r="I6" s="54"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="84"/>
-      <c r="D7" s="85" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="87"/>
+      <c r="C7" s="78"/>
+      <c r="D7" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="81"/>
     </row>
     <row r="8" spans="2:9" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="76" t="s">
+      <c r="D8" s="69"/>
+      <c r="E8" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="82"/>
+      <c r="F8" s="76"/>
       <c r="G8" s="10" t="s">
         <v>26</v>
       </c>
@@ -3201,19 +3444,19 @@
       <c r="B9" s="47">
         <v>1</v>
       </c>
-      <c r="C9" s="66" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="67"/>
+      <c r="C9" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" s="58"/>
       <c r="E9" s="59" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F9" s="60"/>
       <c r="G9" s="8" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>23</v>
@@ -3223,42 +3466,36 @@
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
       <c r="H10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="56"/>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="58"/>
+      <c r="C11" s="69"/>
       <c r="D11" s="59" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E11" s="60"/>
       <c r="F11" s="60"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="62"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:I11"/>
@@ -3269,6 +3506,14 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3307,7 +3552,7 @@
       </c>
       <c r="C4" s="92"/>
       <c r="D4" s="100" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E4" s="101"/>
       <c r="F4" s="104"/>
@@ -3318,7 +3563,7 @@
       </c>
       <c r="C5" s="106"/>
       <c r="D5" s="107" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E5" s="108"/>
       <c r="F5" s="109"/>
@@ -3329,7 +3574,7 @@
       </c>
       <c r="C6" s="96"/>
       <c r="D6" s="100" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E6" s="101"/>
       <c r="F6" s="104"/>
@@ -3340,13 +3585,13 @@
       </c>
       <c r="C7" s="94"/>
       <c r="D7" s="55" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E7" s="22" t="s">
         <v>56</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3371,12 +3616,12 @@
     </row>
     <row r="10" spans="2:6" ht="53.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="100" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C10" s="101"/>
       <c r="D10" s="101"/>
       <c r="E10" s="102" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F10" s="103"/>
     </row>
@@ -3411,20 +3656,27 @@
         <v>1</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D13" s="37">
-        <v>46160</v>
+        <v>46133</v>
       </c>
       <c r="E13" s="39" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="40" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:F6"/>
     <mergeCell ref="B3:C3"/>
@@ -3432,13 +3684,6 @@
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3476,7 +3721,7 @@
       </c>
       <c r="C4" s="126"/>
       <c r="D4" s="127" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E4" s="128"/>
       <c r="F4" s="129"/>
@@ -3487,7 +3732,7 @@
       </c>
       <c r="C5" s="126"/>
       <c r="D5" s="127" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E5" s="128"/>
       <c r="F5" s="129"/>
@@ -3523,10 +3768,10 @@
         <v>71</v>
       </c>
       <c r="C8" s="43" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="D8" s="44">
-        <v>46160</v>
+        <v>46133</v>
       </c>
       <c r="E8" s="43" t="s">
         <v>64</v>
@@ -3546,7 +3791,7 @@
     </row>
     <row r="10" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="121" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="C10" s="122"/>
       <c r="D10" s="122"/>
@@ -3565,6 +3810,212 @@
     <mergeCell ref="B6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C5039B7-2FF5-4666-A9B7-CB8E49B2C670}">
+  <dimension ref="E4:L14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="5" spans="5:12" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E5" s="139" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" s="140"/>
+      <c r="G5" s="169">
+        <v>1</v>
+      </c>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="141" t="s">
+        <v>222</v>
+      </c>
+      <c r="L5" s="143"/>
+    </row>
+    <row r="6" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E6" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="145"/>
+      <c r="G6" s="146" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="147" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="148">
+        <v>46132</v>
+      </c>
+      <c r="L6" s="149"/>
+    </row>
+    <row r="7" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E7" s="150" t="s">
+        <v>223</v>
+      </c>
+      <c r="F7" s="151"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="152"/>
+    </row>
+    <row r="8" spans="5:12" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="E8" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="F8" s="154" t="s">
+        <v>225</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="155" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="154" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="154" t="s">
+        <v>227</v>
+      </c>
+      <c r="K8" s="156" t="s">
+        <v>228</v>
+      </c>
+      <c r="L8" s="157" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="5:12" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="158" t="s">
+        <v>230</v>
+      </c>
+      <c r="F9" s="159"/>
+      <c r="G9" s="160" t="s">
+        <v>231</v>
+      </c>
+      <c r="H9" s="160"/>
+      <c r="I9" s="160"/>
+      <c r="J9" s="160"/>
+      <c r="K9" s="160"/>
+      <c r="L9" s="161"/>
+    </row>
+    <row r="10" spans="5:12" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="162" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="151"/>
+      <c r="G10" s="151"/>
+      <c r="H10" s="151"/>
+      <c r="I10" s="151"/>
+      <c r="J10" s="151"/>
+      <c r="K10" s="151"/>
+      <c r="L10" s="152"/>
+    </row>
+    <row r="11" spans="5:12" ht="57" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="158" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" s="159"/>
+      <c r="G11" s="160" t="s">
+        <v>234</v>
+      </c>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
+      <c r="L11" s="161"/>
+    </row>
+    <row r="12" spans="5:12" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="158" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="159"/>
+      <c r="G12" s="160" t="s">
+        <v>236</v>
+      </c>
+      <c r="H12" s="160"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="160"/>
+      <c r="K12" s="160"/>
+      <c r="L12" s="161"/>
+    </row>
+    <row r="13" spans="5:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="158" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="159"/>
+      <c r="G13" s="163" t="s">
+        <v>238</v>
+      </c>
+      <c r="H13" s="163"/>
+      <c r="I13" s="163"/>
+      <c r="J13" s="147" t="s">
+        <v>239</v>
+      </c>
+      <c r="K13" s="160" t="s">
+        <v>240</v>
+      </c>
+      <c r="L13" s="161"/>
+    </row>
+    <row r="14" spans="5:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="164" t="s">
+        <v>241</v>
+      </c>
+      <c r="F14" s="165"/>
+      <c r="G14" s="166" t="s">
+        <v>242</v>
+      </c>
+      <c r="H14" s="167">
+        <v>46133</v>
+      </c>
+      <c r="I14" s="166" t="s">
+        <v>243</v>
+      </c>
+      <c r="J14" s="167">
+        <v>46133</v>
+      </c>
+      <c r="K14" s="166" t="s">
+        <v>244</v>
+      </c>
+      <c r="L14" s="168"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:L12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E7:L7"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:L9"/>
+    <mergeCell ref="E10:L10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:L11"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="K6:L6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3583,42 +4034,42 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="3:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="64"/>
+      <c r="E4" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
       <c r="H4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="J4" s="67"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="77" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="3:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="58"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="59" t="s">
         <v>37</v>
       </c>
@@ -3627,16 +4078,16 @@
       <c r="H6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="61">
         <v>46087</v>
       </c>
-      <c r="J6" s="70"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="74"/>
       <c r="E7" s="14" t="s">
         <v>34</v>
       </c>
@@ -3657,31 +4108,31 @@
       </c>
     </row>
     <row r="8" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="85" t="s">
+      <c r="D8" s="78"/>
+      <c r="E8" s="79" t="s">
         <v>200</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="87"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="76" t="s">
+      <c r="E9" s="69"/>
+      <c r="F9" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="82"/>
+      <c r="G9" s="76"/>
       <c r="H9" s="10" t="s">
         <v>26</v>
       </c>
@@ -3696,10 +4147,10 @@
       <c r="C10" s="46">
         <v>1</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="57" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="67"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="59" t="s">
         <v>150</v>
       </c>
@@ -3718,10 +4169,10 @@
       <c r="C11" s="46">
         <v>2</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="57" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="67"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="59" t="s">
         <v>151</v>
       </c>
@@ -3740,10 +4191,10 @@
       <c r="C12" s="46">
         <v>3</v>
       </c>
-      <c r="D12" s="66" t="s">
+      <c r="D12" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="E12" s="67"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="59" t="s">
         <v>152</v>
       </c>
@@ -3762,10 +4213,10 @@
       <c r="C13" s="46">
         <v>4</v>
       </c>
-      <c r="D13" s="66" t="s">
+      <c r="D13" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="67"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="59" t="s">
         <v>153</v>
       </c>
@@ -3784,14 +4235,14 @@
       <c r="C14" s="46">
         <v>5</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="E14" s="67"/>
-      <c r="F14" s="66" t="s">
+      <c r="E14" s="58"/>
+      <c r="F14" s="57" t="s">
         <v>154</v>
       </c>
-      <c r="G14" s="68"/>
+      <c r="G14" s="87"/>
       <c r="H14" s="8" t="s">
         <v>134</v>
       </c>
@@ -3806,10 +4257,10 @@
       <c r="C15" s="46">
         <v>6</v>
       </c>
-      <c r="D15" s="66" t="s">
+      <c r="D15" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="67"/>
+      <c r="E15" s="58"/>
       <c r="F15" s="59" t="s">
         <v>155</v>
       </c>
@@ -3828,10 +4279,10 @@
       <c r="C16" s="46">
         <v>7</v>
       </c>
-      <c r="D16" s="66" t="s">
+      <c r="D16" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="67"/>
+      <c r="E16" s="58"/>
       <c r="F16" s="59" t="s">
         <v>156</v>
       </c>
@@ -3850,34 +4301,49 @@
       <c r="C17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="65"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="86"/>
       <c r="I17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="3:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="58"/>
+      <c r="D18" s="69"/>
       <c r="E18" s="59" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="60"/>
       <c r="G18" s="60"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="62"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:J18"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="I6:J6"/>
@@ -3893,21 +4359,6 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:J8"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:J18"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4443,42 +4894,42 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="3:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="64"/>
+      <c r="E4" s="65" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
       <c r="H4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="67"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="77" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="3:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="58"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="59" t="s">
         <v>37</v>
       </c>
@@ -4487,16 +4938,16 @@
       <c r="H6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="61">
         <v>46087</v>
       </c>
-      <c r="J6" s="70"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="74"/>
       <c r="E7" s="14" t="s">
         <v>34</v>
       </c>
@@ -4517,31 +4968,31 @@
       </c>
     </row>
     <row r="8" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="85" t="s">
+      <c r="D8" s="78"/>
+      <c r="E8" s="79" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="87"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="76" t="s">
+      <c r="E9" s="69"/>
+      <c r="F9" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="82"/>
+      <c r="G9" s="76"/>
       <c r="H9" s="10" t="s">
         <v>26</v>
       </c>
@@ -4552,14 +5003,14 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="3:10" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:10" ht="174" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C10" s="47">
         <v>1</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="E10" s="67"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="59" t="s">
         <v>121</v>
       </c>
@@ -4574,14 +5025,14 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="3:10" ht="95.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:10" ht="130.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="47">
         <v>2</v>
       </c>
-      <c r="D11" s="66" t="s">
+      <c r="D11" s="57" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="67"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="59" t="s">
         <v>124</v>
       </c>
@@ -4600,43 +5051,34 @@
       <c r="C12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
       <c r="I12" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="3:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="58"/>
+      <c r="D13" s="69"/>
       <c r="E13" s="59" t="s">
         <v>166</v>
       </c>
       <c r="F13" s="60"/>
       <c r="G13" s="60"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="62"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="E13:J13"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="I6:J6"/>
@@ -4648,6 +5090,15 @@
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:G6"/>
     <mergeCell ref="C7:D7"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E13:J13"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5008,42 +5459,42 @@
   <sheetData>
     <row r="3" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="3:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="72"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="64"/>
+      <c r="E4" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="75"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="67"/>
       <c r="H4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="J4" s="67"/>
+      <c r="J4" s="58"/>
     </row>
     <row r="5" spans="3:10" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="77" t="s">
+      <c r="D5" s="69"/>
+      <c r="E5" s="70" t="s">
         <v>188</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="72"/>
     </row>
     <row r="6" spans="3:10" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="76" t="s">
+      <c r="C6" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="58"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="59" t="s">
         <v>37</v>
       </c>
@@ -5052,16 +5503,16 @@
       <c r="H6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="61">
         <v>46087</v>
       </c>
-      <c r="J6" s="70"/>
+      <c r="J6" s="62"/>
     </row>
     <row r="7" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="80" t="s">
+      <c r="C7" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="81"/>
+      <c r="D7" s="74"/>
       <c r="E7" s="14" t="s">
         <v>34</v>
       </c>
@@ -5082,31 +5533,31 @@
       </c>
     </row>
     <row r="8" spans="3:10" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="84"/>
-      <c r="E8" s="85" t="s">
+      <c r="D8" s="78"/>
+      <c r="E8" s="79" t="s">
         <v>189</v>
       </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="86"/>
-      <c r="H8" s="86"/>
-      <c r="I8" s="86"/>
-      <c r="J8" s="87"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="80"/>
+      <c r="J8" s="81"/>
     </row>
     <row r="9" spans="3:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C9" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="57" t="s">
+      <c r="D9" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="76" t="s">
+      <c r="E9" s="69"/>
+      <c r="F9" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="82"/>
+      <c r="G9" s="76"/>
       <c r="H9" s="10" t="s">
         <v>26</v>
       </c>
@@ -5121,10 +5572,10 @@
       <c r="C10" s="47">
         <v>1</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="57" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="67"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="59" t="s">
         <v>90</v>
       </c>
@@ -5143,31 +5594,31 @@
       <c r="C11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
       <c r="I11" s="5" t="s">
         <v>20</v>
       </c>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="3:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="58"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="59" t="s">
         <v>175</v>
       </c>
       <c r="F12" s="60"/>
       <c r="G12" s="60"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="62"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="83"/>
     </row>
     <row r="13" spans="3:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="2"/>
@@ -5195,6 +5646,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:J12"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:J8"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:G4"/>
@@ -5203,16 +5664,6 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="E6:G6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:J8"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:J12"/>
-    <mergeCell ref="D11:H11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
